--- a/SGC-CKN/Excel/b94e1ac4-9285-4715-a516-e153e21aa4e0_Lô_đất_ký_hiệu_CT-02_P11-50_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/b94e1ac4-9285-4715-a516-e153e21aa4e0_Lô_đất_ký_hiệu_CT-02_P11-50_D800_19-03-2026.xlsx
@@ -135,7 +135,7 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">00:40
+    <t xml:space="preserve">00:00
 19/03/2026</t>
   </si>
   <si>
@@ -165,7 +165,7 @@
     <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">03:07
+    <t xml:space="preserve">03:04
 19/03/2026</t>
   </si>
   <si>
@@ -1262,13 +1262,13 @@
         <v>-28.2</v>
       </c>
       <c r="H14" s="16">
-        <v>1.5</v>
+        <v>0.83</v>
       </c>
       <c r="I14" s="16">
         <v>10.7</v>
       </c>
       <c r="J14" s="12">
-        <v>7.13</v>
+        <v>12.84</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1297,13 +1297,13 @@
         <v>-35</v>
       </c>
       <c r="H15" s="19">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I15" s="19">
         <v>6.8</v>
       </c>
       <c r="J15" s="12">
-        <v>20.4</v>
+        <v>6.8</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1367,13 +1367,13 @@
         <v>-44.25</v>
       </c>
       <c r="H17" s="25">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="I17" s="25">
         <v>6.75</v>
       </c>
       <c r="J17" s="12">
-        <v>7.11</v>
+        <v>7.5</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>49</v>
@@ -1402,13 +1402,13 @@
         <v>-50.08</v>
       </c>
       <c r="H18" s="28">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="I18" s="28">
         <v>5.83</v>
       </c>
       <c r="J18" s="8">
-        <v>3.57</v>
+        <v>3.46</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>53</v>
@@ -1656,13 +1656,13 @@
         <v>-28.2</v>
       </c>
       <c r="G5" s="16">
-        <v>1.5</v>
+        <v>0.83</v>
       </c>
       <c r="H5" s="16">
         <v>10.7</v>
       </c>
       <c r="I5" s="12">
-        <v>7.13</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1685,13 +1685,13 @@
         <v>-35</v>
       </c>
       <c r="G6" s="19">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="H6" s="19">
         <v>6.8</v>
       </c>
       <c r="I6" s="12">
-        <v>20.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1743,13 +1743,13 @@
         <v>-44.25</v>
       </c>
       <c r="G8" s="25">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H8" s="25">
         <v>6.75</v>
       </c>
       <c r="I8" s="12">
-        <v>7.11</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1772,13 +1772,13 @@
         <v>-50.08</v>
       </c>
       <c r="G9" s="28">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="H9" s="28">
         <v>5.83</v>
       </c>
       <c r="I9" s="8">
-        <v>3.57</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
